--- a/Team-Data/2013-14/3-14-2013-14.xlsx
+++ b/Team-Data/2013-14/3-14-2013-14.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -739,16 +806,16 @@
         <v>-0.9</v>
       </c>
       <c r="AD2" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AE2" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AF2" t="n">
         <v>18</v>
       </c>
       <c r="AG2" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AH2" t="n">
         <v>10</v>
@@ -757,7 +824,7 @@
         <v>18</v>
       </c>
       <c r="AJ2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AK2" t="n">
         <v>9</v>
@@ -778,13 +845,13 @@
         <v>22</v>
       </c>
       <c r="AQ2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AR2" t="n">
         <v>28</v>
       </c>
       <c r="AS2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AT2" t="n">
         <v>28</v>
@@ -793,7 +860,7 @@
         <v>1</v>
       </c>
       <c r="AV2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AW2" t="n">
         <v>8</v>
@@ -808,7 +875,7 @@
         <v>4</v>
       </c>
       <c r="BA2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BB2" t="n">
         <v>13</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>3-14-2013-14</t>
+          <t>2014-03-14</t>
         </is>
       </c>
     </row>
@@ -843,37 +910,37 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E3" t="n">
         <v>22</v>
       </c>
       <c r="F3" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G3" t="n">
-        <v>0.333</v>
+        <v>0.338</v>
       </c>
       <c r="H3" t="n">
         <v>48.1</v>
       </c>
       <c r="I3" t="n">
-        <v>36.2</v>
+        <v>36.3</v>
       </c>
       <c r="J3" t="n">
-        <v>83.90000000000001</v>
+        <v>83.7</v>
       </c>
       <c r="K3" t="n">
-        <v>0.432</v>
+        <v>0.434</v>
       </c>
       <c r="L3" t="n">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="M3" t="n">
-        <v>19.9</v>
+        <v>19.8</v>
       </c>
       <c r="N3" t="n">
-        <v>0.323</v>
+        <v>0.326</v>
       </c>
       <c r="O3" t="n">
         <v>16.3</v>
@@ -882,19 +949,19 @@
         <v>21.2</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.771</v>
+        <v>0.769</v>
       </c>
       <c r="R3" t="n">
-        <v>12</v>
+        <v>11.9</v>
       </c>
       <c r="S3" t="n">
-        <v>31.1</v>
+        <v>31</v>
       </c>
       <c r="T3" t="n">
-        <v>43.1</v>
+        <v>42.9</v>
       </c>
       <c r="U3" t="n">
-        <v>20.4</v>
+        <v>20.5</v>
       </c>
       <c r="V3" t="n">
         <v>15.4</v>
@@ -915,13 +982,13 @@
         <v>19.3</v>
       </c>
       <c r="AB3" t="n">
-        <v>95.2</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="AC3" t="n">
         <v>-4</v>
       </c>
       <c r="AD3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AE3" t="n">
         <v>25</v>
@@ -942,49 +1009,49 @@
         <v>11</v>
       </c>
       <c r="AK3" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AL3" t="n">
         <v>24</v>
       </c>
       <c r="AM3" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AN3" t="n">
         <v>28</v>
       </c>
       <c r="AO3" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AP3" t="n">
         <v>25</v>
       </c>
       <c r="AQ3" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AR3" t="n">
         <v>7</v>
       </c>
       <c r="AS3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AT3" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AU3" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AV3" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AW3" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AX3" t="n">
         <v>21</v>
       </c>
       <c r="AY3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AZ3" t="n">
         <v>19</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>3-14-2013-14</t>
+          <t>2014-03-14</t>
         </is>
       </c>
     </row>
@@ -1103,10 +1170,10 @@
         <v>-1.3</v>
       </c>
       <c r="AD4" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AE4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AF4" t="n">
         <v>14</v>
@@ -1136,7 +1203,7 @@
         <v>13</v>
       </c>
       <c r="AO4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AP4" t="n">
         <v>11</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>3-14-2013-14</t>
+          <t>2014-03-14</t>
         </is>
       </c>
     </row>
@@ -1207,28 +1274,28 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E5" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F5" t="n">
         <v>34</v>
       </c>
       <c r="G5" t="n">
-        <v>0.485</v>
+        <v>0.477</v>
       </c>
       <c r="H5" t="n">
         <v>48.3</v>
       </c>
       <c r="I5" t="n">
-        <v>35.9</v>
+        <v>35.7</v>
       </c>
       <c r="J5" t="n">
-        <v>81.5</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="K5" t="n">
-        <v>0.44</v>
+        <v>0.439</v>
       </c>
       <c r="L5" t="n">
         <v>6</v>
@@ -1237,28 +1304,28 @@
         <v>17</v>
       </c>
       <c r="N5" t="n">
-        <v>0.352</v>
+        <v>0.351</v>
       </c>
       <c r="O5" t="n">
-        <v>18.1</v>
+        <v>18.2</v>
       </c>
       <c r="P5" t="n">
-        <v>24.7</v>
+        <v>24.8</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.732</v>
+        <v>0.733</v>
       </c>
       <c r="R5" t="n">
-        <v>9.1</v>
+        <v>9</v>
       </c>
       <c r="S5" t="n">
-        <v>32.9</v>
+        <v>32.8</v>
       </c>
       <c r="T5" t="n">
-        <v>42</v>
+        <v>41.8</v>
       </c>
       <c r="U5" t="n">
-        <v>21.1</v>
+        <v>21</v>
       </c>
       <c r="V5" t="n">
         <v>12.5</v>
@@ -1270,25 +1337,25 @@
         <v>5.1</v>
       </c>
       <c r="Y5" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="Z5" t="n">
         <v>18.2</v>
       </c>
       <c r="AA5" t="n">
-        <v>21</v>
+        <v>21.1</v>
       </c>
       <c r="AB5" t="n">
-        <v>95.8</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="AC5" t="n">
-        <v>-1.4</v>
+        <v>-1.6</v>
       </c>
       <c r="AD5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AE5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AF5" t="n">
         <v>17</v>
@@ -1300,34 +1367,34 @@
         <v>17</v>
       </c>
       <c r="AI5" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AJ5" t="n">
         <v>24</v>
       </c>
       <c r="AK5" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AL5" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AM5" t="n">
         <v>28</v>
       </c>
       <c r="AN5" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AO5" t="n">
         <v>12</v>
       </c>
       <c r="AP5" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AQ5" t="n">
         <v>24</v>
       </c>
       <c r="AR5" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AS5" t="n">
         <v>9</v>
@@ -1348,19 +1415,19 @@
         <v>11</v>
       </c>
       <c r="AY5" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AZ5" t="n">
         <v>2</v>
       </c>
       <c r="BA5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BB5" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BC5" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BD5" t="n">
         <v>10</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>3-14-2013-14</t>
+          <t>2014-03-14</t>
         </is>
       </c>
     </row>
@@ -1467,10 +1534,10 @@
         <v>1.1</v>
       </c>
       <c r="AD6" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="AE6" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AF6" t="n">
         <v>13</v>
@@ -1479,7 +1546,7 @@
         <v>13</v>
       </c>
       <c r="AH6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI6" t="n">
         <v>30</v>
@@ -1488,7 +1555,7 @@
         <v>27</v>
       </c>
       <c r="AK6" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AL6" t="n">
         <v>26</v>
@@ -1509,7 +1576,7 @@
         <v>9</v>
       </c>
       <c r="AR6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AS6" t="n">
         <v>8</v>
@@ -1524,10 +1591,10 @@
         <v>26</v>
       </c>
       <c r="AW6" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AX6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AY6" t="n">
         <v>29</v>
@@ -1536,7 +1603,7 @@
         <v>5</v>
       </c>
       <c r="BA6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BB6" t="n">
         <v>30</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>3-14-2013-14</t>
+          <t>2014-03-14</t>
         </is>
       </c>
     </row>
@@ -1571,22 +1638,22 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E7" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F7" t="n">
         <v>40</v>
       </c>
       <c r="G7" t="n">
-        <v>0.394</v>
+        <v>0.385</v>
       </c>
       <c r="H7" t="n">
         <v>48.7</v>
       </c>
       <c r="I7" t="n">
-        <v>36.5</v>
+        <v>36.4</v>
       </c>
       <c r="J7" t="n">
         <v>85.2</v>
@@ -1601,22 +1668,22 @@
         <v>19.9</v>
       </c>
       <c r="N7" t="n">
-        <v>0.357</v>
+        <v>0.355</v>
       </c>
       <c r="O7" t="n">
         <v>17.2</v>
       </c>
       <c r="P7" t="n">
-        <v>22.8</v>
+        <v>22.9</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.752</v>
+        <v>0.753</v>
       </c>
       <c r="R7" t="n">
-        <v>12.5</v>
+        <v>12.6</v>
       </c>
       <c r="S7" t="n">
-        <v>31.9</v>
+        <v>31.8</v>
       </c>
       <c r="T7" t="n">
         <v>44.4</v>
@@ -1628,7 +1695,7 @@
         <v>14.4</v>
       </c>
       <c r="W7" t="n">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="X7" t="n">
         <v>3.8</v>
@@ -1646,22 +1713,22 @@
         <v>97.2</v>
       </c>
       <c r="AC7" t="n">
-        <v>-4.2</v>
+        <v>-4.4</v>
       </c>
       <c r="AD7" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AE7" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AF7" t="n">
         <v>21</v>
       </c>
       <c r="AG7" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AH7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AI7" t="n">
         <v>23</v>
@@ -1703,10 +1770,10 @@
         <v>25</v>
       </c>
       <c r="AV7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AW7" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AX7" t="n">
         <v>29</v>
@@ -1715,7 +1782,7 @@
         <v>27</v>
       </c>
       <c r="AZ7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA7" t="n">
         <v>22</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>3-14-2013-14</t>
+          <t>2014-03-14</t>
         </is>
       </c>
     </row>
@@ -1831,25 +1898,25 @@
         <v>1.9</v>
       </c>
       <c r="AD8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AE8" t="n">
         <v>9</v>
       </c>
       <c r="AF8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AH8" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AI8" t="n">
         <v>2</v>
       </c>
       <c r="AJ8" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AK8" t="n">
         <v>6</v>
@@ -1876,7 +1943,7 @@
         <v>23</v>
       </c>
       <c r="AS8" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AT8" t="n">
         <v>27</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>3-14-2013-14</t>
+          <t>2014-03-14</t>
         </is>
       </c>
     </row>
@@ -1935,16 +2002,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E9" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F9" t="n">
         <v>36</v>
       </c>
       <c r="G9" t="n">
-        <v>0.446</v>
+        <v>0.438</v>
       </c>
       <c r="H9" t="n">
         <v>48.2</v>
@@ -1953,7 +2020,7 @@
         <v>38.2</v>
       </c>
       <c r="J9" t="n">
-        <v>85.40000000000001</v>
+        <v>85.5</v>
       </c>
       <c r="K9" t="n">
         <v>0.447</v>
@@ -1968,13 +2035,13 @@
         <v>0.361</v>
       </c>
       <c r="O9" t="n">
-        <v>18.9</v>
+        <v>18.8</v>
       </c>
       <c r="P9" t="n">
         <v>26.3</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.719</v>
+        <v>0.716</v>
       </c>
       <c r="R9" t="n">
         <v>12.3</v>
@@ -1983,7 +2050,7 @@
         <v>33</v>
       </c>
       <c r="T9" t="n">
-        <v>45.3</v>
+        <v>45.4</v>
       </c>
       <c r="U9" t="n">
         <v>22.1</v>
@@ -1992,10 +2059,10 @@
         <v>15.7</v>
       </c>
       <c r="W9" t="n">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="X9" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="Y9" t="n">
         <v>5.6</v>
@@ -2004,16 +2071,16 @@
         <v>23</v>
       </c>
       <c r="AA9" t="n">
-        <v>21.6</v>
+        <v>21.7</v>
       </c>
       <c r="AB9" t="n">
-        <v>103.7</v>
+        <v>103.6</v>
       </c>
       <c r="AC9" t="n">
-        <v>-2.1</v>
+        <v>-2.2</v>
       </c>
       <c r="AD9" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="AE9" t="n">
         <v>18</v>
@@ -2022,10 +2089,10 @@
         <v>19</v>
       </c>
       <c r="AG9" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AH9" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AI9" t="n">
         <v>12</v>
@@ -2034,7 +2101,7 @@
         <v>5</v>
       </c>
       <c r="AK9" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AL9" t="n">
         <v>10</v>
@@ -2043,7 +2110,7 @@
         <v>9</v>
       </c>
       <c r="AN9" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AO9" t="n">
         <v>8</v>
@@ -2061,7 +2128,7 @@
         <v>7</v>
       </c>
       <c r="AT9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AU9" t="n">
         <v>12</v>
@@ -2070,10 +2137,10 @@
         <v>27</v>
       </c>
       <c r="AW9" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AX9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AY9" t="n">
         <v>24</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>3-14-2013-14</t>
+          <t>2014-03-14</t>
         </is>
       </c>
     </row>
@@ -2195,19 +2262,19 @@
         <v>-2.9</v>
       </c>
       <c r="AD10" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="AE10" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AF10" t="n">
         <v>21</v>
       </c>
       <c r="AG10" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AH10" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AI10" t="n">
         <v>8</v>
@@ -2216,7 +2283,7 @@
         <v>4</v>
       </c>
       <c r="AK10" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AL10" t="n">
         <v>29</v>
@@ -2249,7 +2316,7 @@
         <v>21</v>
       </c>
       <c r="AV10" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AW10" t="n">
         <v>5</v>
@@ -2258,7 +2325,7 @@
         <v>7</v>
       </c>
       <c r="AY10" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AZ10" t="n">
         <v>15</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>3-14-2013-14</t>
+          <t>2014-03-14</t>
         </is>
       </c>
     </row>
@@ -2299,16 +2366,16 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E11" t="n">
         <v>41</v>
       </c>
       <c r="F11" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G11" t="n">
-        <v>0.612</v>
+        <v>0.621</v>
       </c>
       <c r="H11" t="n">
         <v>48.3</v>
@@ -2317,16 +2384,16 @@
         <v>39</v>
       </c>
       <c r="J11" t="n">
-        <v>85</v>
+        <v>85.2</v>
       </c>
       <c r="K11" t="n">
         <v>0.458</v>
       </c>
       <c r="L11" t="n">
-        <v>9.199999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="M11" t="n">
-        <v>24.3</v>
+        <v>24.2</v>
       </c>
       <c r="N11" t="n">
         <v>0.377</v>
@@ -2335,19 +2402,19 @@
         <v>16.3</v>
       </c>
       <c r="P11" t="n">
-        <v>21.8</v>
+        <v>21.9</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.745</v>
+        <v>0.746</v>
       </c>
       <c r="R11" t="n">
-        <v>11.1</v>
+        <v>11.2</v>
       </c>
       <c r="S11" t="n">
-        <v>34.3</v>
+        <v>34.2</v>
       </c>
       <c r="T11" t="n">
-        <v>45.3</v>
+        <v>45.4</v>
       </c>
       <c r="U11" t="n">
         <v>23.2</v>
@@ -2371,10 +2438,10 @@
         <v>20</v>
       </c>
       <c r="AB11" t="n">
-        <v>103.4</v>
+        <v>103.5</v>
       </c>
       <c r="AC11" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="AD11" t="n">
         <v>1</v>
@@ -2392,7 +2459,7 @@
         <v>18</v>
       </c>
       <c r="AI11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AJ11" t="n">
         <v>7</v>
@@ -2410,7 +2477,7 @@
         <v>6</v>
       </c>
       <c r="AO11" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AP11" t="n">
         <v>20</v>
@@ -2419,25 +2486,25 @@
         <v>23</v>
       </c>
       <c r="AR11" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AS11" t="n">
         <v>3</v>
       </c>
       <c r="AT11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AU11" t="n">
         <v>8</v>
       </c>
       <c r="AV11" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AW11" t="n">
         <v>13</v>
       </c>
       <c r="AX11" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AY11" t="n">
         <v>10</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>3-14-2013-14</t>
+          <t>2014-03-14</t>
         </is>
       </c>
     </row>
@@ -2559,7 +2626,7 @@
         <v>4.4</v>
       </c>
       <c r="AD12" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="AE12" t="n">
         <v>5</v>
@@ -2571,7 +2638,7 @@
         <v>6</v>
       </c>
       <c r="AH12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AI12" t="n">
         <v>17</v>
@@ -2589,7 +2656,7 @@
         <v>1</v>
       </c>
       <c r="AN12" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AO12" t="n">
         <v>1</v>
@@ -2607,7 +2674,7 @@
         <v>4</v>
       </c>
       <c r="AT12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AU12" t="n">
         <v>22</v>
@@ -2616,25 +2683,25 @@
         <v>29</v>
       </c>
       <c r="AW12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AX12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AY12" t="n">
         <v>22</v>
       </c>
       <c r="AZ12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BA12" t="n">
         <v>1</v>
       </c>
       <c r="BB12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BC12" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BD12" t="n">
         <v>10</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>3-14-2013-14</t>
+          <t>2014-03-14</t>
         </is>
       </c>
     </row>
@@ -2663,28 +2730,28 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E13" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F13" t="n">
         <v>17</v>
       </c>
       <c r="G13" t="n">
-        <v>0.738</v>
+        <v>0.734</v>
       </c>
       <c r="H13" t="n">
         <v>48.2</v>
       </c>
       <c r="I13" t="n">
-        <v>36.8</v>
+        <v>36.7</v>
       </c>
       <c r="J13" t="n">
-        <v>80.59999999999999</v>
+        <v>80.8</v>
       </c>
       <c r="K13" t="n">
-        <v>0.456</v>
+        <v>0.455</v>
       </c>
       <c r="L13" t="n">
         <v>6.8</v>
@@ -2693,40 +2760,40 @@
         <v>19.2</v>
       </c>
       <c r="N13" t="n">
-        <v>0.354</v>
+        <v>0.353</v>
       </c>
       <c r="O13" t="n">
-        <v>18.2</v>
+        <v>18.3</v>
       </c>
       <c r="P13" t="n">
-        <v>23.3</v>
+        <v>23.4</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.78</v>
+        <v>0.783</v>
       </c>
       <c r="R13" t="n">
-        <v>10.2</v>
+        <v>10.3</v>
       </c>
       <c r="S13" t="n">
-        <v>35</v>
+        <v>34.9</v>
       </c>
       <c r="T13" t="n">
         <v>45.1</v>
       </c>
       <c r="U13" t="n">
-        <v>20.4</v>
+        <v>20.3</v>
       </c>
       <c r="V13" t="n">
-        <v>15.4</v>
+        <v>15.3</v>
       </c>
       <c r="W13" t="n">
         <v>7</v>
       </c>
       <c r="X13" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="Y13" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="Z13" t="n">
         <v>20.3</v>
@@ -2735,22 +2802,22 @@
         <v>21.9</v>
       </c>
       <c r="AB13" t="n">
-        <v>98.59999999999999</v>
+        <v>98.5</v>
       </c>
       <c r="AC13" t="n">
         <v>6.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="AE13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF13" t="n">
         <v>2</v>
       </c>
       <c r="AG13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AH13" t="n">
         <v>19</v>
@@ -2762,7 +2829,7 @@
         <v>26</v>
       </c>
       <c r="AK13" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AL13" t="n">
         <v>22</v>
@@ -2771,7 +2838,7 @@
         <v>24</v>
       </c>
       <c r="AN13" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AO13" t="n">
         <v>11</v>
@@ -2780,7 +2847,7 @@
         <v>14</v>
       </c>
       <c r="AQ13" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AR13" t="n">
         <v>22</v>
@@ -2792,16 +2859,16 @@
         <v>7</v>
       </c>
       <c r="AU13" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AV13" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="AW13" t="n">
         <v>24</v>
       </c>
       <c r="AX13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AY13" t="n">
         <v>13</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>3-14-2013-14</t>
+          <t>2014-03-14</t>
         </is>
       </c>
     </row>
@@ -2845,16 +2912,16 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E14" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F14" t="n">
         <v>20</v>
       </c>
       <c r="G14" t="n">
-        <v>0.701</v>
+        <v>0.697</v>
       </c>
       <c r="H14" t="n">
         <v>48.2</v>
@@ -2863,10 +2930,10 @@
         <v>39.1</v>
       </c>
       <c r="J14" t="n">
-        <v>82</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="K14" t="n">
-        <v>0.477</v>
+        <v>0.476</v>
       </c>
       <c r="L14" t="n">
         <v>8.199999999999999</v>
@@ -2878,28 +2945,28 @@
         <v>0.352</v>
       </c>
       <c r="O14" t="n">
-        <v>21.3</v>
+        <v>21.4</v>
       </c>
       <c r="P14" t="n">
-        <v>29.3</v>
+        <v>29.4</v>
       </c>
       <c r="Q14" t="n">
         <v>0.728</v>
       </c>
       <c r="R14" t="n">
-        <v>10.4</v>
+        <v>10.5</v>
       </c>
       <c r="S14" t="n">
-        <v>32.6</v>
+        <v>32.7</v>
       </c>
       <c r="T14" t="n">
-        <v>43</v>
+        <v>43.2</v>
       </c>
       <c r="U14" t="n">
-        <v>24.3</v>
+        <v>24.4</v>
       </c>
       <c r="V14" t="n">
-        <v>14</v>
+        <v>14.1</v>
       </c>
       <c r="W14" t="n">
         <v>8.5</v>
@@ -2911,13 +2978,13 @@
         <v>3.3</v>
       </c>
       <c r="Z14" t="n">
-        <v>21.6</v>
+        <v>21.7</v>
       </c>
       <c r="AA14" t="n">
-        <v>23.8</v>
+        <v>23.9</v>
       </c>
       <c r="AB14" t="n">
-        <v>107.7</v>
+        <v>107.9</v>
       </c>
       <c r="AC14" t="n">
         <v>7.2</v>
@@ -2932,7 +2999,7 @@
         <v>5</v>
       </c>
       <c r="AG14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AH14" t="n">
         <v>23</v>
@@ -2941,7 +3008,7 @@
         <v>5</v>
       </c>
       <c r="AJ14" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AK14" t="n">
         <v>3</v>
@@ -2953,7 +3020,7 @@
         <v>8</v>
       </c>
       <c r="AN14" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AO14" t="n">
         <v>3</v>
@@ -2962,16 +3029,16 @@
         <v>2</v>
       </c>
       <c r="AQ14" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AR14" t="n">
         <v>21</v>
       </c>
       <c r="AS14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AT14" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AU14" t="n">
         <v>3</v>
@@ -2983,7 +3050,7 @@
         <v>7</v>
       </c>
       <c r="AX14" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AY14" t="n">
         <v>2</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>3-14-2013-14</t>
+          <t>2014-03-14</t>
         </is>
       </c>
     </row>
@@ -3027,37 +3094,37 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E15" t="n">
         <v>22</v>
       </c>
       <c r="F15" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G15" t="n">
-        <v>0.333</v>
+        <v>0.338</v>
       </c>
       <c r="H15" t="n">
         <v>48.1</v>
       </c>
       <c r="I15" t="n">
-        <v>37.7</v>
+        <v>37.8</v>
       </c>
       <c r="J15" t="n">
-        <v>84.40000000000001</v>
+        <v>84.3</v>
       </c>
       <c r="K15" t="n">
-        <v>0.447</v>
+        <v>0.449</v>
       </c>
       <c r="L15" t="n">
-        <v>9.4</v>
+        <v>9.5</v>
       </c>
       <c r="M15" t="n">
         <v>24.7</v>
       </c>
       <c r="N15" t="n">
-        <v>0.382</v>
+        <v>0.385</v>
       </c>
       <c r="O15" t="n">
         <v>16.9</v>
@@ -3081,10 +3148,10 @@
         <v>23.8</v>
       </c>
       <c r="V15" t="n">
-        <v>15.4</v>
+        <v>15.5</v>
       </c>
       <c r="W15" t="n">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="X15" t="n">
         <v>5.7</v>
@@ -3093,19 +3160,19 @@
         <v>4.6</v>
       </c>
       <c r="Z15" t="n">
-        <v>20</v>
+        <v>20.1</v>
       </c>
       <c r="AA15" t="n">
         <v>19.5</v>
       </c>
       <c r="AB15" t="n">
-        <v>101.8</v>
+        <v>102</v>
       </c>
       <c r="AC15" t="n">
-        <v>-6.7</v>
+        <v>-6.2</v>
       </c>
       <c r="AD15" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AE15" t="n">
         <v>25</v>
@@ -3120,13 +3187,13 @@
         <v>28</v>
       </c>
       <c r="AI15" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AJ15" t="n">
         <v>9</v>
       </c>
       <c r="AK15" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AL15" t="n">
         <v>2</v>
@@ -3144,10 +3211,10 @@
         <v>19</v>
       </c>
       <c r="AQ15" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AR15" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AS15" t="n">
         <v>13</v>
@@ -3159,7 +3226,7 @@
         <v>4</v>
       </c>
       <c r="AV15" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AW15" t="n">
         <v>26</v>
@@ -3174,7 +3241,7 @@
         <v>10</v>
       </c>
       <c r="BA15" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BB15" t="n">
         <v>12</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>3-14-2013-14</t>
+          <t>2014-03-14</t>
         </is>
       </c>
     </row>
@@ -3209,85 +3276,85 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E16" t="n">
         <v>38</v>
       </c>
       <c r="F16" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G16" t="n">
-        <v>0.585</v>
+        <v>0.594</v>
       </c>
       <c r="H16" t="n">
         <v>48.3</v>
       </c>
       <c r="I16" t="n">
-        <v>37.7</v>
+        <v>37.8</v>
       </c>
       <c r="J16" t="n">
-        <v>81.8</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="K16" t="n">
-        <v>0.461</v>
+        <v>0.462</v>
       </c>
       <c r="L16" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="M16" t="n">
-        <v>14.1</v>
+        <v>14.2</v>
       </c>
       <c r="N16" t="n">
-        <v>0.357</v>
+        <v>0.358</v>
       </c>
       <c r="O16" t="n">
         <v>15.2</v>
       </c>
       <c r="P16" t="n">
-        <v>20.3</v>
+        <v>20.2</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.749</v>
+        <v>0.751</v>
       </c>
       <c r="R16" t="n">
         <v>11.4</v>
       </c>
       <c r="S16" t="n">
-        <v>30.8</v>
+        <v>30.9</v>
       </c>
       <c r="T16" t="n">
-        <v>42.2</v>
+        <v>42.3</v>
       </c>
       <c r="U16" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="V16" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="W16" t="n">
         <v>7.7</v>
       </c>
       <c r="X16" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="Y16" t="n">
         <v>5.3</v>
       </c>
       <c r="Z16" t="n">
-        <v>19.3</v>
+        <v>19.4</v>
       </c>
       <c r="AA16" t="n">
-        <v>19</v>
+        <v>18.9</v>
       </c>
       <c r="AB16" t="n">
-        <v>95.7</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="AC16" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="AD16" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="AE16" t="n">
         <v>10</v>
@@ -3296,16 +3363,16 @@
         <v>9</v>
       </c>
       <c r="AG16" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AH16" t="n">
         <v>16</v>
       </c>
       <c r="AI16" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AJ16" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AK16" t="n">
         <v>7</v>
@@ -3323,10 +3390,10 @@
         <v>29</v>
       </c>
       <c r="AP16" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AQ16" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AR16" t="n">
         <v>14</v>
@@ -3335,13 +3402,13 @@
         <v>22</v>
       </c>
       <c r="AT16" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AU16" t="n">
         <v>15</v>
       </c>
       <c r="AV16" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW16" t="n">
         <v>16</v>
@@ -3359,7 +3426,7 @@
         <v>29</v>
       </c>
       <c r="BB16" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BC16" t="n">
         <v>14</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>3-14-2013-14</t>
+          <t>2014-03-14</t>
         </is>
       </c>
     </row>
@@ -3391,16 +3458,16 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E17" t="n">
         <v>44</v>
       </c>
       <c r="F17" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G17" t="n">
-        <v>0.698</v>
+        <v>0.71</v>
       </c>
       <c r="H17" t="n">
         <v>48.5</v>
@@ -3418,16 +3485,16 @@
         <v>8.1</v>
       </c>
       <c r="M17" t="n">
-        <v>21.9</v>
+        <v>21.8</v>
       </c>
       <c r="N17" t="n">
-        <v>0.37</v>
+        <v>0.371</v>
       </c>
       <c r="O17" t="n">
         <v>17.8</v>
       </c>
       <c r="P17" t="n">
-        <v>23.3</v>
+        <v>23.4</v>
       </c>
       <c r="Q17" t="n">
         <v>0.762</v>
@@ -3445,7 +3512,7 @@
         <v>23.1</v>
       </c>
       <c r="V17" t="n">
-        <v>14.9</v>
+        <v>14.8</v>
       </c>
       <c r="W17" t="n">
         <v>9.1</v>
@@ -3466,10 +3533,10 @@
         <v>103.9</v>
       </c>
       <c r="AC17" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="AD17" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AE17" t="n">
         <v>5</v>
@@ -3478,13 +3545,13 @@
         <v>4</v>
       </c>
       <c r="AG17" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AH17" t="n">
         <v>9</v>
       </c>
       <c r="AI17" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AJ17" t="n">
         <v>30</v>
@@ -3496,7 +3563,7 @@
         <v>14</v>
       </c>
       <c r="AM17" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AN17" t="n">
         <v>11</v>
@@ -3523,7 +3590,7 @@
         <v>10</v>
       </c>
       <c r="AV17" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AW17" t="n">
         <v>2</v>
@@ -3535,7 +3602,7 @@
         <v>1</v>
       </c>
       <c r="AZ17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BA17" t="n">
         <v>15</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>3-14-2013-14</t>
+          <t>2014-03-14</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3718,7 @@
         <v>-8</v>
       </c>
       <c r="AD18" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="AE18" t="n">
         <v>30</v>
@@ -3663,7 +3730,7 @@
         <v>30</v>
       </c>
       <c r="AH18" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AI18" t="n">
         <v>28</v>
@@ -3681,7 +3748,7 @@
         <v>19</v>
       </c>
       <c r="AN18" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AO18" t="n">
         <v>25</v>
@@ -3693,7 +3760,7 @@
         <v>16</v>
       </c>
       <c r="AR18" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AS18" t="n">
         <v>28</v>
@@ -3711,10 +3778,10 @@
         <v>28</v>
       </c>
       <c r="AX18" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AY18" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AZ18" t="n">
         <v>18</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>3-14-2013-14</t>
+          <t>2014-03-14</t>
         </is>
       </c>
     </row>
@@ -3755,16 +3822,16 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E19" t="n">
         <v>32</v>
       </c>
       <c r="F19" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G19" t="n">
-        <v>0.5</v>
+        <v>0.508</v>
       </c>
       <c r="H19" t="n">
         <v>48.2</v>
@@ -3773,7 +3840,7 @@
         <v>38.6</v>
       </c>
       <c r="J19" t="n">
-        <v>87.7</v>
+        <v>87.8</v>
       </c>
       <c r="K19" t="n">
         <v>0.44</v>
@@ -3782,34 +3849,34 @@
         <v>7.4</v>
       </c>
       <c r="M19" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="O19" t="n">
         <v>21.7</v>
       </c>
-      <c r="N19" t="n">
-        <v>0.341</v>
-      </c>
-      <c r="O19" t="n">
-        <v>21.6</v>
-      </c>
       <c r="P19" t="n">
-        <v>27.8</v>
+        <v>27.9</v>
       </c>
       <c r="Q19" t="n">
         <v>0.777</v>
       </c>
       <c r="R19" t="n">
-        <v>12.8</v>
+        <v>12.9</v>
       </c>
       <c r="S19" t="n">
         <v>32.5</v>
       </c>
       <c r="T19" t="n">
-        <v>45.3</v>
+        <v>45.4</v>
       </c>
       <c r="U19" t="n">
         <v>23.3</v>
       </c>
       <c r="V19" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="W19" t="n">
         <v>8.699999999999999</v>
@@ -3821,16 +3888,16 @@
         <v>5.8</v>
       </c>
       <c r="Z19" t="n">
-        <v>18.5</v>
+        <v>18.6</v>
       </c>
       <c r="AA19" t="n">
-        <v>23.6</v>
+        <v>23.7</v>
       </c>
       <c r="AB19" t="n">
-        <v>106.1</v>
+        <v>106.3</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="AD19" t="n">
         <v>26</v>
@@ -3839,7 +3906,7 @@
         <v>16</v>
       </c>
       <c r="AF19" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AG19" t="n">
         <v>16</v>
@@ -3848,19 +3915,19 @@
         <v>24</v>
       </c>
       <c r="AI19" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AJ19" t="n">
         <v>2</v>
       </c>
       <c r="AK19" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AL19" t="n">
         <v>17</v>
       </c>
       <c r="AM19" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AN19" t="n">
         <v>26</v>
@@ -3881,13 +3948,13 @@
         <v>12</v>
       </c>
       <c r="AT19" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AU19" t="n">
         <v>6</v>
       </c>
       <c r="AV19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AW19" t="n">
         <v>4</v>
@@ -3905,7 +3972,7 @@
         <v>3</v>
       </c>
       <c r="BB19" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="BC19" t="n">
         <v>9</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>3-14-2013-14</t>
+          <t>2014-03-14</t>
         </is>
       </c>
     </row>
@@ -3937,16 +4004,16 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E20" t="n">
         <v>26</v>
       </c>
       <c r="F20" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G20" t="n">
-        <v>0.4</v>
+        <v>0.406</v>
       </c>
       <c r="H20" t="n">
         <v>48.4</v>
@@ -3955,10 +4022,10 @@
         <v>37.9</v>
       </c>
       <c r="J20" t="n">
-        <v>83</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="K20" t="n">
-        <v>0.457</v>
+        <v>0.456</v>
       </c>
       <c r="L20" t="n">
         <v>6</v>
@@ -3967,19 +4034,19 @@
         <v>16</v>
       </c>
       <c r="N20" t="n">
-        <v>0.375</v>
+        <v>0.376</v>
       </c>
       <c r="O20" t="n">
         <v>17.7</v>
       </c>
       <c r="P20" t="n">
-        <v>22.9</v>
+        <v>23</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.77</v>
+        <v>0.769</v>
       </c>
       <c r="R20" t="n">
-        <v>11.8</v>
+        <v>11.9</v>
       </c>
       <c r="S20" t="n">
         <v>30.2</v>
@@ -3997,7 +4064,7 @@
         <v>8</v>
       </c>
       <c r="X20" t="n">
-        <v>6.3</v>
+        <v>6.4</v>
       </c>
       <c r="Y20" t="n">
         <v>6</v>
@@ -4009,13 +4076,13 @@
         <v>20</v>
       </c>
       <c r="AB20" t="n">
-        <v>99.5</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="AC20" t="n">
-        <v>-2.6</v>
+        <v>-2.5</v>
       </c>
       <c r="AD20" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="AE20" t="n">
         <v>20</v>
@@ -4039,13 +4106,13 @@
         <v>11</v>
       </c>
       <c r="AL20" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AM20" t="n">
         <v>29</v>
       </c>
       <c r="AN20" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AO20" t="n">
         <v>15</v>
@@ -4060,7 +4127,7 @@
         <v>8</v>
       </c>
       <c r="AS20" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AT20" t="n">
         <v>21</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>3-14-2013-14</t>
+          <t>2014-03-14</t>
         </is>
       </c>
     </row>
@@ -4197,7 +4264,7 @@
         <v>-1.6</v>
       </c>
       <c r="AD21" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AE21" t="n">
         <v>20</v>
@@ -4224,10 +4291,10 @@
         <v>5</v>
       </c>
       <c r="AM21" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AN21" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AO21" t="n">
         <v>30</v>
@@ -4236,7 +4303,7 @@
         <v>30</v>
       </c>
       <c r="AQ21" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AR21" t="n">
         <v>19</v>
@@ -4248,7 +4315,7 @@
         <v>26</v>
       </c>
       <c r="AU21" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AV21" t="n">
         <v>2</v>
@@ -4272,7 +4339,7 @@
         <v>20</v>
       </c>
       <c r="BC21" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BD21" t="n">
         <v>10</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>3-14-2013-14</t>
+          <t>2014-03-14</t>
         </is>
       </c>
     </row>
@@ -4379,10 +4446,10 @@
         <v>6.9</v>
       </c>
       <c r="AD22" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="AE22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AF22" t="n">
         <v>2</v>
@@ -4391,7 +4458,7 @@
         <v>2</v>
       </c>
       <c r="AH22" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AI22" t="n">
         <v>4</v>
@@ -4409,19 +4476,19 @@
         <v>16</v>
       </c>
       <c r="AN22" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AO22" t="n">
         <v>5</v>
       </c>
       <c r="AP22" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AQ22" t="n">
         <v>2</v>
       </c>
       <c r="AR22" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AS22" t="n">
         <v>2</v>
@@ -4436,7 +4503,7 @@
         <v>28</v>
       </c>
       <c r="AW22" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AX22" t="n">
         <v>2</v>
@@ -4451,10 +4518,10 @@
         <v>18</v>
       </c>
       <c r="BB22" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BC22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BD22" t="n">
         <v>10</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>3-14-2013-14</t>
+          <t>2014-03-14</t>
         </is>
       </c>
     </row>
@@ -4483,25 +4550,25 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E23" t="n">
         <v>19</v>
       </c>
       <c r="F23" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G23" t="n">
-        <v>0.284</v>
+        <v>0.288</v>
       </c>
       <c r="H23" t="n">
         <v>48.7</v>
       </c>
       <c r="I23" t="n">
-        <v>37.1</v>
+        <v>37</v>
       </c>
       <c r="J23" t="n">
-        <v>83.59999999999999</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="K23" t="n">
         <v>0.444</v>
@@ -4510,16 +4577,16 @@
         <v>6.9</v>
       </c>
       <c r="M23" t="n">
-        <v>19.9</v>
+        <v>19.8</v>
       </c>
       <c r="N23" t="n">
-        <v>0.348</v>
+        <v>0.349</v>
       </c>
       <c r="O23" t="n">
-        <v>16</v>
+        <v>16.1</v>
       </c>
       <c r="P23" t="n">
-        <v>20.8</v>
+        <v>21</v>
       </c>
       <c r="Q23" t="n">
         <v>0.767</v>
@@ -4531,16 +4598,16 @@
         <v>32.7</v>
       </c>
       <c r="T23" t="n">
-        <v>42.3</v>
+        <v>42.2</v>
       </c>
       <c r="U23" t="n">
-        <v>21</v>
+        <v>20.9</v>
       </c>
       <c r="V23" t="n">
         <v>14.4</v>
       </c>
       <c r="W23" t="n">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="X23" t="n">
         <v>4.2</v>
@@ -4552,10 +4619,10 @@
         <v>20.2</v>
       </c>
       <c r="AA23" t="n">
-        <v>18.5</v>
+        <v>18.6</v>
       </c>
       <c r="AB23" t="n">
-        <v>97.09999999999999</v>
+        <v>97</v>
       </c>
       <c r="AC23" t="n">
         <v>-5.2</v>
@@ -4573,13 +4640,13 @@
         <v>28</v>
       </c>
       <c r="AH23" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AI23" t="n">
         <v>20</v>
       </c>
       <c r="AJ23" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AK23" t="n">
         <v>21</v>
@@ -4588,7 +4655,7 @@
         <v>20</v>
       </c>
       <c r="AM23" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AN23" t="n">
         <v>24</v>
@@ -4597,7 +4664,7 @@
         <v>26</v>
       </c>
       <c r="AP23" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AQ23" t="n">
         <v>13</v>
@@ -4606,16 +4673,16 @@
         <v>24</v>
       </c>
       <c r="AS23" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AT23" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AU23" t="n">
         <v>20</v>
       </c>
       <c r="AV23" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AW23" t="n">
         <v>14</v>
@@ -4627,7 +4694,7 @@
         <v>25</v>
       </c>
       <c r="AZ23" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA23" t="n">
         <v>30</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>3-14-2013-14</t>
+          <t>2014-03-14</t>
         </is>
       </c>
     </row>
@@ -4665,34 +4732,34 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E24" t="n">
         <v>15</v>
       </c>
       <c r="F24" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G24" t="n">
-        <v>0.231</v>
+        <v>0.234</v>
       </c>
       <c r="H24" t="n">
         <v>48.5</v>
       </c>
       <c r="I24" t="n">
-        <v>38</v>
+        <v>38.1</v>
       </c>
       <c r="J24" t="n">
         <v>88</v>
       </c>
       <c r="K24" t="n">
-        <v>0.432</v>
+        <v>0.433</v>
       </c>
       <c r="L24" t="n">
         <v>6.8</v>
       </c>
       <c r="M24" t="n">
-        <v>22.1</v>
+        <v>22</v>
       </c>
       <c r="N24" t="n">
         <v>0.306</v>
@@ -4701,49 +4768,49 @@
         <v>16.9</v>
       </c>
       <c r="P24" t="n">
-        <v>23.5</v>
+        <v>23.6</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.719</v>
+        <v>0.717</v>
       </c>
       <c r="R24" t="n">
         <v>11.8</v>
       </c>
       <c r="S24" t="n">
-        <v>31.6</v>
+        <v>31.8</v>
       </c>
       <c r="T24" t="n">
-        <v>43.4</v>
+        <v>43.6</v>
       </c>
       <c r="U24" t="n">
         <v>22</v>
       </c>
       <c r="V24" t="n">
-        <v>17.3</v>
+        <v>17.5</v>
       </c>
       <c r="W24" t="n">
         <v>9.300000000000001</v>
       </c>
       <c r="X24" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="Y24" t="n">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="Z24" t="n">
-        <v>22</v>
+        <v>22.1</v>
       </c>
       <c r="AA24" t="n">
         <v>20.9</v>
       </c>
       <c r="AB24" t="n">
-        <v>99.7</v>
+        <v>99.8</v>
       </c>
       <c r="AC24" t="n">
-        <v>-11.2</v>
+        <v>-11.3</v>
       </c>
       <c r="AD24" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="AE24" t="n">
         <v>29</v>
@@ -4755,7 +4822,7 @@
         <v>29</v>
       </c>
       <c r="AH24" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AI24" t="n">
         <v>13</v>
@@ -4764,7 +4831,7 @@
         <v>1</v>
       </c>
       <c r="AK24" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AL24" t="n">
         <v>23</v>
@@ -4785,7 +4852,7 @@
         <v>27</v>
       </c>
       <c r="AR24" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AS24" t="n">
         <v>16</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>3-14-2013-14</t>
+          <t>2014-03-14</t>
         </is>
       </c>
     </row>
@@ -4847,58 +4914,58 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E25" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F25" t="n">
         <v>28</v>
       </c>
       <c r="G25" t="n">
-        <v>0.569</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="H25" t="n">
         <v>48.2</v>
       </c>
       <c r="I25" t="n">
-        <v>38.6</v>
+        <v>38.7</v>
       </c>
       <c r="J25" t="n">
-        <v>84</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="K25" t="n">
         <v>0.46</v>
       </c>
       <c r="L25" t="n">
-        <v>9.300000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="M25" t="n">
         <v>25.1</v>
       </c>
       <c r="N25" t="n">
-        <v>0.371</v>
+        <v>0.374</v>
       </c>
       <c r="O25" t="n">
-        <v>18.6</v>
+        <v>18.7</v>
       </c>
       <c r="P25" t="n">
-        <v>24.6</v>
+        <v>24.7</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.756</v>
+        <v>0.757</v>
       </c>
       <c r="R25" t="n">
         <v>11.6</v>
       </c>
       <c r="S25" t="n">
-        <v>31.6</v>
+        <v>31.5</v>
       </c>
       <c r="T25" t="n">
-        <v>43.2</v>
+        <v>43.1</v>
       </c>
       <c r="U25" t="n">
-        <v>19.3</v>
+        <v>19.4</v>
       </c>
       <c r="V25" t="n">
         <v>15.3</v>
@@ -4913,19 +4980,19 @@
         <v>4.2</v>
       </c>
       <c r="Z25" t="n">
-        <v>22</v>
+        <v>22.1</v>
       </c>
       <c r="AA25" t="n">
         <v>21.4</v>
       </c>
       <c r="AB25" t="n">
-        <v>105.2</v>
+        <v>105.5</v>
       </c>
       <c r="AC25" t="n">
         <v>2.4</v>
       </c>
       <c r="AD25" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="AE25" t="n">
         <v>11</v>
@@ -4949,16 +5016,16 @@
         <v>8</v>
       </c>
       <c r="AL25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AM25" t="n">
         <v>3</v>
       </c>
       <c r="AN25" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AO25" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AP25" t="n">
         <v>10</v>
@@ -4973,7 +5040,7 @@
         <v>17</v>
       </c>
       <c r="AT25" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AU25" t="n">
         <v>29</v>
@@ -4985,13 +5052,13 @@
         <v>9</v>
       </c>
       <c r="AX25" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AY25" t="n">
         <v>9</v>
       </c>
       <c r="AZ25" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BA25" t="n">
         <v>8</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>3-14-2013-14</t>
+          <t>2014-03-14</t>
         </is>
       </c>
     </row>
@@ -5029,37 +5096,37 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E26" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F26" t="n">
         <v>23</v>
       </c>
       <c r="G26" t="n">
-        <v>0.652</v>
+        <v>0.646</v>
       </c>
       <c r="H26" t="n">
         <v>48.4</v>
       </c>
       <c r="I26" t="n">
-        <v>39.3</v>
+        <v>39.4</v>
       </c>
       <c r="J26" t="n">
-        <v>87.5</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="K26" t="n">
-        <v>0.45</v>
+        <v>0.449</v>
       </c>
       <c r="L26" t="n">
-        <v>9.4</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="M26" t="n">
-        <v>25</v>
+        <v>24.8</v>
       </c>
       <c r="N26" t="n">
-        <v>0.375</v>
+        <v>0.374</v>
       </c>
       <c r="O26" t="n">
         <v>19.2</v>
@@ -5071,13 +5138,13 @@
         <v>0.8179999999999999</v>
       </c>
       <c r="R26" t="n">
-        <v>12.7</v>
+        <v>12.8</v>
       </c>
       <c r="S26" t="n">
         <v>33.7</v>
       </c>
       <c r="T26" t="n">
-        <v>46.4</v>
+        <v>46.6</v>
       </c>
       <c r="U26" t="n">
         <v>23.2</v>
@@ -5098,16 +5165,16 @@
         <v>19.7</v>
       </c>
       <c r="AA26" t="n">
-        <v>20.7</v>
+        <v>20.6</v>
       </c>
       <c r="AB26" t="n">
-        <v>107.3</v>
+        <v>107.2</v>
       </c>
       <c r="AC26" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="AD26" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AE26" t="n">
         <v>7</v>
@@ -5119,7 +5186,7 @@
         <v>7</v>
       </c>
       <c r="AH26" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AI26" t="n">
         <v>3</v>
@@ -5131,13 +5198,13 @@
         <v>15</v>
       </c>
       <c r="AL26" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AM26" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AN26" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AO26" t="n">
         <v>6</v>
@@ -5152,7 +5219,7 @@
         <v>3</v>
       </c>
       <c r="AS26" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AT26" t="n">
         <v>1</v>
@@ -5170,7 +5237,7 @@
         <v>13</v>
       </c>
       <c r="AY26" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AZ26" t="n">
         <v>7</v>
@@ -5182,7 +5249,7 @@
         <v>2</v>
       </c>
       <c r="BC26" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BD26" t="n">
         <v>10</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>3-14-2013-14</t>
+          <t>2014-03-14</t>
         </is>
       </c>
     </row>
@@ -5289,7 +5356,7 @@
         <v>-2.3</v>
       </c>
       <c r="AD27" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="AE27" t="n">
         <v>24</v>
@@ -5301,7 +5368,7 @@
         <v>24</v>
       </c>
       <c r="AH27" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AI27" t="n">
         <v>21</v>
@@ -5310,7 +5377,7 @@
         <v>18</v>
       </c>
       <c r="AK27" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AL27" t="n">
         <v>25</v>
@@ -5328,7 +5395,7 @@
         <v>4</v>
       </c>
       <c r="AQ27" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AR27" t="n">
         <v>6</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>3-14-2013-14</t>
+          <t>2014-03-14</t>
         </is>
       </c>
     </row>
@@ -5393,25 +5460,25 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E28" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F28" t="n">
         <v>16</v>
       </c>
       <c r="G28" t="n">
-        <v>0.754</v>
+        <v>0.75</v>
       </c>
       <c r="H28" t="n">
         <v>48.2</v>
       </c>
       <c r="I28" t="n">
-        <v>40.3</v>
+        <v>40.2</v>
       </c>
       <c r="J28" t="n">
-        <v>82.5</v>
+        <v>82.3</v>
       </c>
       <c r="K28" t="n">
         <v>0.488</v>
@@ -5420,31 +5487,31 @@
         <v>8.300000000000001</v>
       </c>
       <c r="M28" t="n">
-        <v>20.9</v>
+        <v>20.8</v>
       </c>
       <c r="N28" t="n">
-        <v>0.398</v>
+        <v>0.396</v>
       </c>
       <c r="O28" t="n">
         <v>16</v>
       </c>
       <c r="P28" t="n">
-        <v>20.3</v>
+        <v>20.4</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.787</v>
+        <v>0.788</v>
       </c>
       <c r="R28" t="n">
-        <v>9.1</v>
+        <v>9</v>
       </c>
       <c r="S28" t="n">
-        <v>33.8</v>
+        <v>33.7</v>
       </c>
       <c r="T28" t="n">
-        <v>42.9</v>
+        <v>42.6</v>
       </c>
       <c r="U28" t="n">
-        <v>25.1</v>
+        <v>24.9</v>
       </c>
       <c r="V28" t="n">
         <v>14.8</v>
@@ -5453,7 +5520,7 @@
         <v>7.4</v>
       </c>
       <c r="X28" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="Y28" t="n">
         <v>4.7</v>
@@ -5462,16 +5529,16 @@
         <v>18.1</v>
       </c>
       <c r="AA28" t="n">
-        <v>19.5</v>
+        <v>19.6</v>
       </c>
       <c r="AB28" t="n">
-        <v>104.8</v>
+        <v>104.6</v>
       </c>
       <c r="AC28" t="n">
-        <v>7.1</v>
+        <v>6.7</v>
       </c>
       <c r="AD28" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="AE28" t="n">
         <v>1</v>
@@ -5489,7 +5556,7 @@
         <v>1</v>
       </c>
       <c r="AJ28" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AK28" t="n">
         <v>2</v>
@@ -5507,7 +5574,7 @@
         <v>27</v>
       </c>
       <c r="AP28" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AQ28" t="n">
         <v>4</v>
@@ -5516,7 +5583,7 @@
         <v>27</v>
       </c>
       <c r="AS28" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AT28" t="n">
         <v>17</v>
@@ -5540,13 +5607,13 @@
         <v>1</v>
       </c>
       <c r="BA28" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BB28" t="n">
         <v>7</v>
       </c>
       <c r="BC28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BD28" t="n">
         <v>10</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>3-14-2013-14</t>
+          <t>2014-03-14</t>
         </is>
       </c>
     </row>
@@ -5575,16 +5642,16 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E29" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F29" t="n">
         <v>27</v>
       </c>
       <c r="G29" t="n">
-        <v>0.578</v>
+        <v>0.571</v>
       </c>
       <c r="H29" t="n">
         <v>48.6</v>
@@ -5593,19 +5660,19 @@
         <v>36.3</v>
       </c>
       <c r="J29" t="n">
-        <v>82</v>
+        <v>82.2</v>
       </c>
       <c r="K29" t="n">
-        <v>0.443</v>
+        <v>0.442</v>
       </c>
       <c r="L29" t="n">
         <v>8.4</v>
       </c>
       <c r="M29" t="n">
-        <v>22.8</v>
+        <v>22.9</v>
       </c>
       <c r="N29" t="n">
-        <v>0.369</v>
+        <v>0.368</v>
       </c>
       <c r="O29" t="n">
         <v>19.2</v>
@@ -5614,28 +5681,28 @@
         <v>24.7</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.777</v>
+        <v>0.776</v>
       </c>
       <c r="R29" t="n">
-        <v>11.6</v>
+        <v>11.7</v>
       </c>
       <c r="S29" t="n">
         <v>31.4</v>
       </c>
       <c r="T29" t="n">
-        <v>43</v>
+        <v>43.1</v>
       </c>
       <c r="U29" t="n">
         <v>21.3</v>
       </c>
       <c r="V29" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="W29" t="n">
         <v>7</v>
       </c>
       <c r="X29" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="Y29" t="n">
         <v>4.4</v>
@@ -5650,7 +5717,7 @@
         <v>100.3</v>
       </c>
       <c r="AC29" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="AD29" t="n">
         <v>26</v>
@@ -5659,7 +5726,7 @@
         <v>11</v>
       </c>
       <c r="AF29" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG29" t="n">
         <v>11</v>
@@ -5674,7 +5741,7 @@
         <v>20</v>
       </c>
       <c r="AK29" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AL29" t="n">
         <v>9</v>
@@ -5689,7 +5756,7 @@
         <v>7</v>
       </c>
       <c r="AP29" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AQ29" t="n">
         <v>8</v>
@@ -5698,10 +5765,10 @@
         <v>12</v>
       </c>
       <c r="AS29" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AT29" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AU29" t="n">
         <v>17</v>
@@ -5716,7 +5783,7 @@
         <v>22</v>
       </c>
       <c r="AY29" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ29" t="n">
         <v>29</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>3-14-2013-14</t>
+          <t>2014-03-14</t>
         </is>
       </c>
     </row>
@@ -5757,16 +5824,16 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E30" t="n">
         <v>22</v>
       </c>
       <c r="F30" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G30" t="n">
-        <v>0.333</v>
+        <v>0.338</v>
       </c>
       <c r="H30" t="n">
         <v>48.2</v>
@@ -5784,34 +5851,34 @@
         <v>6.8</v>
       </c>
       <c r="M30" t="n">
-        <v>19.3</v>
+        <v>19.4</v>
       </c>
       <c r="N30" t="n">
-        <v>0.353</v>
+        <v>0.352</v>
       </c>
       <c r="O30" t="n">
-        <v>16.3</v>
+        <v>16.4</v>
       </c>
       <c r="P30" t="n">
-        <v>21.7</v>
+        <v>21.9</v>
       </c>
       <c r="Q30" t="n">
         <v>0.748</v>
       </c>
       <c r="R30" t="n">
-        <v>10.9</v>
+        <v>11</v>
       </c>
       <c r="S30" t="n">
         <v>30.6</v>
       </c>
       <c r="T30" t="n">
-        <v>41.5</v>
+        <v>41.6</v>
       </c>
       <c r="U30" t="n">
         <v>20</v>
       </c>
       <c r="V30" t="n">
-        <v>14.8</v>
+        <v>14.7</v>
       </c>
       <c r="W30" t="n">
         <v>6.8</v>
@@ -5826,16 +5893,16 @@
         <v>20.8</v>
       </c>
       <c r="AA30" t="n">
-        <v>20.3</v>
+        <v>20.4</v>
       </c>
       <c r="AB30" t="n">
-        <v>94.7</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="AC30" t="n">
         <v>-6</v>
       </c>
       <c r="AD30" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AE30" t="n">
         <v>25</v>
@@ -5847,16 +5914,16 @@
         <v>25</v>
       </c>
       <c r="AH30" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AI30" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AJ30" t="n">
         <v>25</v>
       </c>
       <c r="AK30" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AL30" t="n">
         <v>21</v>
@@ -5865,10 +5932,10 @@
         <v>23</v>
       </c>
       <c r="AN30" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AO30" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AP30" t="n">
         <v>21</v>
@@ -5889,7 +5956,7 @@
         <v>28</v>
       </c>
       <c r="AV30" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AW30" t="n">
         <v>27</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>3-14-2013-14</t>
+          <t>2014-03-14</t>
         </is>
       </c>
     </row>
@@ -5939,19 +6006,19 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E31" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F31" t="n">
         <v>31</v>
       </c>
       <c r="G31" t="n">
-        <v>0.523</v>
+        <v>0.516</v>
       </c>
       <c r="H31" t="n">
-        <v>49</v>
+        <v>48.9</v>
       </c>
       <c r="I31" t="n">
         <v>38.6</v>
@@ -5960,55 +6027,55 @@
         <v>84.8</v>
       </c>
       <c r="K31" t="n">
-        <v>0.455</v>
+        <v>0.456</v>
       </c>
       <c r="L31" t="n">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="M31" t="n">
         <v>20.8</v>
       </c>
       <c r="N31" t="n">
-        <v>0.387</v>
+        <v>0.386</v>
       </c>
       <c r="O31" t="n">
-        <v>15.3</v>
+        <v>15.2</v>
       </c>
       <c r="P31" t="n">
-        <v>21</v>
+        <v>20.9</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.729</v>
+        <v>0.727</v>
       </c>
       <c r="R31" t="n">
         <v>11</v>
       </c>
       <c r="S31" t="n">
-        <v>31.5</v>
+        <v>31.3</v>
       </c>
       <c r="T31" t="n">
-        <v>42.5</v>
+        <v>42.3</v>
       </c>
       <c r="U31" t="n">
         <v>23.3</v>
       </c>
       <c r="V31" t="n">
-        <v>14.6</v>
+        <v>14.7</v>
       </c>
       <c r="W31" t="n">
-        <v>8.300000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="X31" t="n">
         <v>4.7</v>
       </c>
       <c r="Y31" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="Z31" t="n">
-        <v>20.5</v>
+        <v>20.6</v>
       </c>
       <c r="AA31" t="n">
-        <v>19.5</v>
+        <v>19.4</v>
       </c>
       <c r="AB31" t="n">
         <v>100.5</v>
@@ -6017,7 +6084,7 @@
         <v>0.6</v>
       </c>
       <c r="AD31" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="AE31" t="n">
         <v>14</v>
@@ -6032,13 +6099,13 @@
         <v>1</v>
       </c>
       <c r="AI31" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AJ31" t="n">
         <v>8</v>
       </c>
       <c r="AK31" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AL31" t="n">
         <v>15</v>
@@ -6053,16 +6120,16 @@
         <v>28</v>
       </c>
       <c r="AP31" t="n">
+        <v>27</v>
+      </c>
+      <c r="AQ31" t="n">
         <v>26</v>
-      </c>
-      <c r="AQ31" t="n">
-        <v>25</v>
       </c>
       <c r="AR31" t="n">
         <v>18</v>
       </c>
       <c r="AS31" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AT31" t="n">
         <v>18</v>
@@ -6071,7 +6138,7 @@
         <v>7</v>
       </c>
       <c r="AV31" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AW31" t="n">
         <v>10</v>
@@ -6086,7 +6153,7 @@
         <v>16</v>
       </c>
       <c r="BA31" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="BB31" t="n">
         <v>16</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>3-14-2013-14</t>
+          <t>2014-03-14</t>
         </is>
       </c>
     </row>
